--- a/astro-site/public/dl/haccp-templates/05-receiving-checklist.xlsx
+++ b/astro-site/public/dl/haccp-templates/05-receiving-checklist.xlsx
@@ -836,7 +836,7 @@
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>Expired / date mark</t>
+          <t>Expiry / date mark</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr">
